--- a/21_Fixed_Income_Rates/_template_FIXED_INCOME.xlsx
+++ b/21_Fixed_Income_Rates/_template_FIXED_INCOME.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Bond Pricing" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Duration &amp; Convexity" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Yield Curve" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="RefreshLog" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Total Return Scenarios" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="RefreshLog" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t xml:space="preserve">[BOND/CURVE] — Fixed Income Model</t>
   </si>
@@ -138,6 +139,24 @@
   </si>
   <si>
     <t xml:space="preserve">Negative = inverted curve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-Year Total Return Under Rate Shocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses duration/convexity from the Duration &amp; Convexity tab plus current yield as the income component — same approximation as that tab's single 100bp estimate, extended across a scenario grid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel shift (bp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price return (duration + convexity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income return (current yield)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total return</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -162,7 +181,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
@@ -171,8 +190,9 @@
     <numFmt numFmtId="169" formatCode="0.00%;\(0.00%\);\-"/>
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="0.00"/>
+    <numFmt numFmtId="172" formatCode="\+0;\-0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,6 +259,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -315,7 +342,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -397,6 +424,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -657,7 +696,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -719,7 +758,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -819,7 +858,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
@@ -907,7 +946,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:E11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14"/>
@@ -1037,8 +1076,168 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <f aca="false">IFERROR(-'Duration &amp; Convexity'!$C$8*(C6/10000)+0.5*'Duration &amp; Convexity'!$C$9*(C6/10000)^2,"-")</f>
+        <v>0.0809674255439289</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <f aca="false">IFERROR(-'Duration &amp; Convexity'!$C$8*(D6/10000)+0.5*'Duration &amp; Convexity'!$C$9*(D6/10000)^2,"-")</f>
+        <v>0.0395746637936784</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <f aca="false">IFERROR(-'Duration &amp; Convexity'!$C$8*(E6/10000)+0.5*'Duration &amp; Convexity'!$C$9*(E6/10000)^2,"-")</f>
+        <v>0.0195600696522677</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <f aca="false">IFERROR(-'Duration &amp; Convexity'!$C$8*(F6/10000)+0.5*'Duration &amp; Convexity'!$C$9*(F6/10000)^2,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <f aca="false">IFERROR(-'Duration &amp; Convexity'!$C$8*(G6/10000)+0.5*'Duration &amp; Convexity'!$C$9*(G6/10000)^2,"-")</f>
+        <v>-0.0191055451631246</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <f aca="false">IFERROR(-'Duration &amp; Convexity'!$C$8*(H6/10000)+0.5*'Duration &amp; Convexity'!$C$9*(H6/10000)^2,"-")</f>
+        <v>-0.0377565658371063</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <f aca="false">IFERROR(-'Duration &amp; Convexity'!$C$8*(I6/10000)+0.5*'Duration &amp; Convexity'!$C$9*(I6/10000)^2,"-")</f>
+        <v>-0.0736950337176404</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <f aca="false">'Bond Pricing'!$C$13</f>
+        <v>0.0519787331896839</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <f aca="false">'Bond Pricing'!$C$13</f>
+        <v>0.0519787331896839</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <f aca="false">'Bond Pricing'!$C$13</f>
+        <v>0.0519787331896839</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <f aca="false">'Bond Pricing'!$C$13</f>
+        <v>0.0519787331896839</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <f aca="false">'Bond Pricing'!$C$13</f>
+        <v>0.0519787331896839</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <f aca="false">'Bond Pricing'!$C$13</f>
+        <v>0.0519787331896839</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <f aca="false">'Bond Pricing'!$C$13</f>
+        <v>0.0519787331896839</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <f aca="false">C7+C8</f>
+        <v>0.132946158733613</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <f aca="false">D7+D8</f>
+        <v>0.0915533969833623</v>
+      </c>
+      <c r="E9" s="23" t="n">
+        <f aca="false">E7+E8</f>
+        <v>0.0715388028419516</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <f aca="false">F7+F8</f>
+        <v>0.0519787331896839</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <f aca="false">G7+G8</f>
+        <v>0.0328731880265593</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <f aca="false">H7+H8</f>
+        <v>0.0142221673525777</v>
+      </c>
+      <c r="I9" s="23" t="n">
+        <f aca="false">I7+I8</f>
+        <v>-0.0217163005279565</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -1049,95 +1248,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/21_Fixed_Income_Rates/_template_FIXED_INCOME.xlsx
+++ b/21_Fixed_Income_Rates/_template_FIXED_INCOME.xlsx
@@ -1,123 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Zero Curve" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Bond Analytics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Portfolio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Key Rate Risk" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Carry &amp; Roll" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Scenarios" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="P&amp;L Explain" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Checks" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Sources" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="RefreshLog" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zero Curve" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bond Analytics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Rate Risk" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carry &amp; Roll" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L Explain" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
     <definedName name="FS_DOMAIN">'Institutional Surface'!$C$5</definedName>
     <definedName name="FS_MATURITY">'Institutional Surface'!$C$6</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="\$#,##0.00;[RED]&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="165" formatCode="0.00%;[RED]\(0.00%\);\-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
+    <numFmt numFmtId="165" formatCode="0.00%;[Red](0.00%);-"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
-    <numFmt numFmtId="168" formatCode="\$#,##0.0;[RED]&quot;($&quot;#,##0.0\);\-"/>
+    <numFmt numFmtId="168" formatCode="$#,##0.0;[Red]($#,##0.0);-"/>
     <numFmt numFmtId="169" formatCode="0.000000"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF111827"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF111827"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF008000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -142,14 +113,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -172,22 +141,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
-        <color rgb="FF111827"/>
+        <color rgb="00111827"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thin">
@@ -195,341 +156,188 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="35">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF111827"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -537,294 +345,404 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="36" customWidth="1" style="31" min="2" max="2"/>
-    <col width="46" customWidth="1" style="31" min="3" max="3"/>
-    <col width="12" customWidth="1" style="31" min="4" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>[PORTFOLIO / SECURITY] — Fixed Income &amp; Rates Model</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="34" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Portfolio / security:</t>
         </is>
       </c>
-      <c r="C4" s="35" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>[Name]</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="34" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Currency / curve:</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>[Currency and benchmark]</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="34" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Last refreshed:</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>[timestamp]</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="34" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Next coupon / auction / event:</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="34" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Refresh cadence:</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="34" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Active scenario:</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="34" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Units:</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>$ in millions; yields in percent</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="36" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Modeling conventions</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="37" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Blue text / yellow fill</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Hardcoded input or selected scenario</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="32">
-      <c r="B15" s="34" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Formula / same-sheet calculation</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="32">
-      <c r="B16" s="39" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Green text</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Cross-sheet formula / link</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="32">
-      <c r="B17" s="34" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Checks</t>
         </is>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>PASS / REVIEW / FAIL must remain visible</t>
         </is>
@@ -836,247 +754,247 @@
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Base,Downside"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="24" customWidth="1" style="31" min="2" max="2"/>
-    <col width="16" customWidth="1" style="31" min="3" max="6"/>
-    <col width="18" customWidth="1" style="31" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>One-Year Carry and Roll-Down</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Coupon carry</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Financing cost</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Yield after roll</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Roll P&amp;L</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Total carry + roll</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31">
+    <row r="5">
+      <c r="B5">
         <f>Portfolio!B5</f>
         <v/>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="20">
         <f>Portfolio!C5*Portfolio!D5</f>
         <v/>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="20">
         <f>Portfolio!C5*Assumptions!E13</f>
         <v/>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="12">
         <f>MAX(0,Portfolio!E5-0.002)</f>
         <v/>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="20">
         <f>Portfolio!C5*Portfolio!I5*(Portfolio!E5-E5)</f>
         <v/>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="20">
         <f>C5-D5+F5</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31">
+    <row r="6">
+      <c r="B6">
         <f>Portfolio!B6</f>
         <v/>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="20">
         <f>Portfolio!C6*Portfolio!D6</f>
         <v/>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="20">
         <f>Portfolio!C6*Assumptions!E13</f>
         <v/>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="12">
         <f>MAX(0,Portfolio!E6-0.002)</f>
         <v/>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="20">
         <f>Portfolio!C6*Portfolio!I6*(Portfolio!E6-E6)</f>
         <v/>
       </c>
-      <c r="G6" s="57">
+      <c r="G6" s="20">
         <f>C6-D6+F6</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31">
+    <row r="7">
+      <c r="B7">
         <f>Portfolio!B7</f>
         <v/>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="20">
         <f>Portfolio!C7*Portfolio!D7</f>
         <v/>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="20">
         <f>Portfolio!C7*Assumptions!E13</f>
         <v/>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="12">
         <f>MAX(0,Portfolio!E7-0.002)</f>
         <v/>
       </c>
-      <c r="F7" s="57">
+      <c r="F7" s="20">
         <f>Portfolio!C7*Portfolio!I7*(Portfolio!E7-E7)</f>
         <v/>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="20">
         <f>C7-D7+F7</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31">
+    <row r="8">
+      <c r="B8">
         <f>Portfolio!B8</f>
         <v/>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="20">
         <f>Portfolio!C8*Portfolio!D8</f>
         <v/>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="20">
         <f>Portfolio!C8*Assumptions!E13</f>
         <v/>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="12">
         <f>MAX(0,Portfolio!E8-0.002)</f>
         <v/>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="20">
         <f>Portfolio!C8*Portfolio!I8*(Portfolio!E8-E8)</f>
         <v/>
       </c>
-      <c r="G8" s="57">
+      <c r="G8" s="20">
         <f>C8-D8+F8</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31">
+    <row r="9">
+      <c r="B9">
         <f>Portfolio!B9</f>
         <v/>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="20">
         <f>Portfolio!C9*Portfolio!D9</f>
         <v/>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="20">
         <f>Portfolio!C9*Assumptions!E13</f>
         <v/>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="12">
         <f>MAX(0,Portfolio!E9-0.002)</f>
         <v/>
       </c>
-      <c r="F9" s="57">
+      <c r="F9" s="20">
         <f>Portfolio!C9*Portfolio!I9*(Portfolio!E9-E9)</f>
         <v/>
       </c>
-      <c r="G9" s="57">
+      <c r="G9" s="20">
         <f>C9-D9+F9</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31">
+    <row r="10">
+      <c r="B10">
         <f>Portfolio!B10</f>
         <v/>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="20">
         <f>Portfolio!C10*Portfolio!D10</f>
         <v/>
       </c>
-      <c r="D10" s="57">
+      <c r="D10" s="20">
         <f>Portfolio!C10*Assumptions!E13</f>
         <v/>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="12">
         <f>MAX(0,Portfolio!E10-0.002)</f>
         <v/>
       </c>
-      <c r="F10" s="57">
+      <c r="F10" s="20">
         <f>Portfolio!C10*Portfolio!I10*(Portfolio!E10-E10)</f>
         <v/>
       </c>
-      <c r="G10" s="57">
+      <c r="G10" s="20">
         <f>C10-D10+F10</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="61" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Portfolio total</t>
         </is>
       </c>
-      <c r="C12" s="62">
+      <c r="C12" s="25">
         <f>SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="25">
         <f>SUM(D5:D10)</f>
         <v/>
       </c>
-      <c r="E12" s="62" t="n"/>
-      <c r="F12" s="62">
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25">
         <f>SUM(F5:F10)</f>
         <v/>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="25">
         <f>SUM(G5:G10)</f>
         <v/>
       </c>
@@ -1085,247 +1003,249 @@
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:I10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="24" customWidth="1" style="31" min="2" max="2"/>
-    <col width="13" customWidth="1" style="31" min="3" max="7"/>
-    <col width="16" customWidth="1" style="31" min="8" max="8"/>
-    <col width="18" customWidth="1" style="31" min="9" max="9"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Curve and Spread Scenarios</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>10Y</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>20Y</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>30Y</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Credit spread</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Estimated P&amp;L</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Parallel +100bp</t>
         </is>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D5" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="F5" s="48" t="n">
+      <c r="F5" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="G5" s="48" t="n">
+      <c r="G5" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="H5" s="48" t="n">
+      <c r="H5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="57">
+      <c r="I5" s="20">
         <f>-SUMPRODUCT('Key Rate Risk'!C12:G12,C5:G5)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H5</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Parallel -100bp</t>
         </is>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F6" s="48" t="n">
+      <c r="F6" s="11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="G6" s="48" t="n">
+      <c r="G6" s="11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="H6" s="48" t="n">
+      <c r="H6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="20">
         <f>-SUMPRODUCT('Key Rate Risk'!C12:G12,C6:G6)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H6</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Bear steepener</t>
         </is>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="11" t="n">
         <v>0.005</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="11" t="n">
         <v>0.008</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="11" t="n">
         <v>0.012</v>
       </c>
-      <c r="F7" s="48" t="n">
+      <c r="F7" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="G7" s="48" t="n">
+      <c r="G7" s="11" t="n">
         <v>0.018</v>
       </c>
-      <c r="H7" s="48" t="n">
+      <c r="H7" s="11" t="n">
         <v>0.002</v>
       </c>
-      <c r="I7" s="57">
+      <c r="I7" s="20">
         <f>-SUMPRODUCT('Key Rate Risk'!C12:G12,C7:G7)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H7</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Bull flattener</t>
         </is>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="11" t="n">
         <v>-0.012</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="D8" s="11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="11" t="n">
         <v>-0.008</v>
       </c>
-      <c r="F8" s="48" t="n">
+      <c r="F8" s="11" t="n">
         <v>-0.006</v>
       </c>
-      <c r="G8" s="48" t="n">
+      <c r="G8" s="11" t="n">
         <v>-0.005</v>
       </c>
-      <c r="H8" s="48" t="n">
+      <c r="H8" s="11" t="n">
         <v>-0.001</v>
       </c>
-      <c r="I8" s="57">
+      <c r="I8" s="20">
         <f>-SUMPRODUCT('Key Rate Risk'!C12:G12,C8:G8)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H8</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Credit widening</t>
         </is>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="11" t="n">
         <v>0.002</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="11" t="n">
         <v>0.003</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="11" t="n">
         <v>0.004</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F9" s="11" t="n">
         <v>0.005</v>
       </c>
-      <c r="G9" s="48" t="n">
+      <c r="G9" s="11" t="n">
         <v>0.005</v>
       </c>
-      <c r="H9" s="48" t="n">
+      <c r="H9" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="I9" s="57">
+      <c r="I9" s="20">
         <f>-SUMPRODUCT('Key Rate Risk'!C12:G12,C9:G9)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H9</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Risk-off rally</t>
         </is>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="11" t="n">
         <v>-0.008</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="11" t="n">
         <v>-0.012</v>
       </c>
-      <c r="F10" s="48" t="n">
+      <c r="F10" s="11" t="n">
         <v>-0.01</v>
       </c>
-      <c r="G10" s="48" t="n">
+      <c r="G10" s="11" t="n">
         <v>-0.008</v>
       </c>
-      <c r="H10" s="48" t="n">
+      <c r="H10" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="I10" s="57">
+      <c r="I10" s="20">
         <f>-SUMPRODUCT('Key Rate Risk'!C12:G12,C10:G10)/0.0001-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)*H10</f>
         <v/>
       </c>
@@ -1334,229 +1254,227 @@
   <mergeCells count="1">
     <mergeCell ref="B2:H2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="22" customWidth="1" style="31" min="2" max="2"/>
-    <col width="18" customWidth="1" style="31" min="3" max="3"/>
-    <col width="16" customWidth="1" style="31" min="4" max="4"/>
-    <col width="18" customWidth="1" style="31" min="5" max="5"/>
-    <col width="38" customWidth="1" style="31" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Rates Portfolio P&amp;L Explain</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Carry</t>
         </is>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="20">
         <f>'Carry &amp; Roll'!C12-'Carry &amp; Roll'!D12</f>
         <v/>
       </c>
-      <c r="D5" s="64" t="n">
+      <c r="D5" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="57">
+      <c r="E5" s="20">
         <f>C5*D5</f>
         <v/>
       </c>
-      <c r="F5" s="31" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>coupon less financing</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Roll-down</t>
         </is>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="20">
         <f>'Carry &amp; Roll'!F12</f>
         <v/>
       </c>
-      <c r="D6" s="64" t="n">
+      <c r="D6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="57">
+      <c r="E6" s="20">
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>curve roll</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Parallel rates</t>
         </is>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="20">
         <f>-Portfolio!K12/0.0001</f>
         <v/>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="11" t="n">
         <v>0.0005</v>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="20">
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>DV01 x move</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Curve shape</t>
         </is>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="20">
         <f>-('Key Rate Risk'!C12*0.0002+'Key Rate Risk'!D12*0.0001-'Key Rate Risk'!F12*0.0001)/0.0001</f>
         <v/>
       </c>
-      <c r="D8" s="64" t="n">
+      <c r="D8" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="20">
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="31" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>key-rate attribution</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Credit spread</t>
         </is>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="20">
         <f>-SUMPRODUCT(Portfolio!C5:C10,Portfolio!G5:G10)</f>
         <v/>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="11" t="n">
         <v>0.0015</v>
       </c>
-      <c r="E9" s="57">
+      <c r="E9" s="20">
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="31" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>spread duration</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Convexity</t>
         </is>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="20">
         <f>0.5*SUMPRODUCT(Portfolio!C5:C10,Portfolio!J5:J10)</f>
         <v/>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="11" t="n">
         <v>2.5e-07</v>
       </c>
-      <c r="E10" s="57">
+      <c r="E10" s="20">
         <f>C10*D10</f>
         <v/>
       </c>
-      <c r="F10" s="31" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>second order</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="31" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Explained P&amp;L</t>
         </is>
       </c>
-      <c r="E13" s="57">
+      <c r="E13" s="20">
         <f>SUM(E5:E10)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="31" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Actual P&amp;L</t>
         </is>
       </c>
-      <c r="E14" s="56" t="n">
+      <c r="E14" s="19" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="32">
-      <c r="B15" s="31" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Unexplained P&amp;L</t>
         </is>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="20">
         <f>E14-E13</f>
         <v/>
       </c>
@@ -1565,129 +1483,127 @@
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="44" customWidth="1" style="31" min="2" max="2"/>
-    <col width="18" customWidth="1" style="31" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Fixed-Income Model Checks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Price positive</t>
         </is>
       </c>
-      <c r="C5" s="31">
+      <c r="C5">
         <f>IF('Bond Analytics'!C5&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Price decreases as yield rises</t>
         </is>
       </c>
-      <c r="C6" s="31">
+      <c r="C6">
         <f>IF('Bond Analytics'!C6&lt;'Bond Analytics'!C5,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Duration positive</t>
         </is>
       </c>
-      <c r="C7" s="31">
+      <c r="C7">
         <f>IF('Bond Analytics'!C8&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Convexity positive</t>
         </is>
       </c>
-      <c r="C8" s="31">
+      <c r="C8">
         <f>IF('Bond Analytics'!C9&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Key-rate DV01 reconciles</t>
         </is>
       </c>
-      <c r="C9" s="31">
-        <f>IF(ABS('Key Rate Risk'!H12-Portfolio!K12)&lt;0.1,"PASS","REVIEW")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+      <c r="C9">
+        <f>IF(ABS('Key Rate Risk'!H12-Portfolio!K12)&lt;0.10,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Curve discount factors decreasing</t>
         </is>
       </c>
-      <c r="C10" s="31">
+      <c r="C10">
         <f>IF(MAX('Zero Curve'!F6:F14-'Zero Curve'!F5:F13)&lt;=0,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="31" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>P&amp;L explain populated</t>
         </is>
       </c>
-      <c r="C11" s="31">
+      <c r="C11">
         <f>IF(COUNT('P&amp;L Explain'!E5:E10)=6,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="31" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="C12" s="31">
+      <c r="C12">
         <f>IF(COUNTIF(C5:C11,"FAIL")=0,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -1697,175 +1613,173 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C12">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>C5="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>C5="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>C5="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>C5="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="34" customWidth="1" style="31" min="2" max="2"/>
-    <col width="58" customWidth="1" style="31" min="3" max="3"/>
-    <col width="16" customWidth="1" style="31" min="4" max="4"/>
-    <col width="48" customWidth="1" style="31" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Source Register</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Input / dataset</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Source URL or document</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Notes / transformation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="65" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Security terms and cash flows</t>
         </is>
       </c>
-      <c r="C5" s="65" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>[prospectus / terms URL]</t>
         </is>
       </c>
-      <c r="D5" s="65" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E5" s="65" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Coupon, maturity, callability, indexation</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="65" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Benchmark and zero curves</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>https://home.treasury.gov/resource-center/data-chart-center/interest-rates</t>
         </is>
       </c>
-      <c r="D6" s="65" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>[timestamp]</t>
         </is>
       </c>
-      <c r="E6" s="65" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>Document interpolation and compounding</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="65" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Credit spreads and prices</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>[market data URL]</t>
         </is>
       </c>
-      <c r="D7" s="65" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>[timestamp]</t>
         </is>
       </c>
-      <c r="E7" s="65" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>Bid/ask, liquidity, source hierarchy</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="65" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Financing and repo</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>[broker / central bank source]</t>
         </is>
       </c>
-      <c r="D8" s="65" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E8" s="65" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Haircuts, specials, term, and currency basis</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="65" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Portfolio positions</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>[OMS / custody source]</t>
         </is>
       </c>
-      <c r="D9" s="65" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>[timestamp]</t>
         </is>
       </c>
-      <c r="E9" s="65" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>Reconcile quantities, accrued interest, and market value</t>
         </is>
@@ -1875,276 +1789,272 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="14" customWidth="1" style="31" min="2" max="2"/>
-    <col width="22" customWidth="1" style="31" min="3" max="3"/>
-    <col width="28" customWidth="1" style="31" min="4" max="4"/>
-    <col width="38" customWidth="1" style="31" min="5" max="5"/>
-    <col width="34" customWidth="1" style="31" min="6" max="6"/>
-    <col width="18" customWidth="1" style="31" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Refresh Log</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Source snapshot</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Reviewer / challenge</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Next check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="66" t="n"/>
-      <c r="C5" s="66" t="n"/>
-      <c r="D5" s="66" t="n"/>
-      <c r="E5" s="66" t="n"/>
-      <c r="F5" s="66" t="n"/>
-      <c r="G5" s="66" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="66" t="n"/>
-      <c r="C6" s="66" t="n"/>
-      <c r="D6" s="66" t="n"/>
-      <c r="E6" s="66" t="n"/>
-      <c r="F6" s="66" t="n"/>
-      <c r="G6" s="66" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="66" t="n"/>
-      <c r="C7" s="66" t="n"/>
-      <c r="D7" s="66" t="n"/>
-      <c r="E7" s="66" t="n"/>
-      <c r="F7" s="66" t="n"/>
-      <c r="G7" s="66" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="66" t="n"/>
-      <c r="C8" s="66" t="n"/>
-      <c r="D8" s="66" t="n"/>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="66" t="n"/>
-      <c r="G8" s="66" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="66" t="n"/>
-      <c r="C9" s="66" t="n"/>
-      <c r="D9" s="66" t="n"/>
-      <c r="E9" s="66" t="n"/>
-      <c r="F9" s="66" t="n"/>
-      <c r="G9" s="66" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="66" t="n"/>
-      <c r="C10" s="66" t="n"/>
-      <c r="D10" s="66" t="n"/>
-      <c r="E10" s="66" t="n"/>
-      <c r="F10" s="66" t="n"/>
-      <c r="G10" s="66" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="66" t="n"/>
-      <c r="C11" s="66" t="n"/>
-      <c r="D11" s="66" t="n"/>
-      <c r="E11" s="66" t="n"/>
-      <c r="F11" s="66" t="n"/>
-      <c r="G11" s="66" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="66" t="n"/>
-      <c r="C12" s="66" t="n"/>
-      <c r="D12" s="66" t="n"/>
-      <c r="E12" s="66" t="n"/>
-      <c r="F12" s="66" t="n"/>
-      <c r="G12" s="66" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="66" t="n"/>
-      <c r="C13" s="66" t="n"/>
-      <c r="D13" s="66" t="n"/>
-      <c r="E13" s="66" t="n"/>
-      <c r="F13" s="66" t="n"/>
-      <c r="G13" s="66" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="66" t="n"/>
-      <c r="C14" s="66" t="n"/>
-      <c r="D14" s="66" t="n"/>
-      <c r="E14" s="66" t="n"/>
-      <c r="F14" s="66" t="n"/>
-      <c r="G14" s="66" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="32">
-      <c r="B15" s="66" t="n"/>
-      <c r="C15" s="66" t="n"/>
-      <c r="D15" s="66" t="n"/>
-      <c r="E15" s="66" t="n"/>
-      <c r="F15" s="66" t="n"/>
-      <c r="G15" s="66" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="32">
-      <c r="B16" s="66" t="n"/>
-      <c r="C16" s="66" t="n"/>
-      <c r="D16" s="66" t="n"/>
-      <c r="E16" s="66" t="n"/>
-      <c r="F16" s="66" t="n"/>
-      <c r="G16" s="66" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="32">
-      <c r="B17" s="66" t="n"/>
-      <c r="C17" s="66" t="n"/>
-      <c r="D17" s="66" t="n"/>
-      <c r="E17" s="66" t="n"/>
-      <c r="F17" s="66" t="n"/>
-      <c r="G17" s="66" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="32">
-      <c r="B18" s="66" t="n"/>
-      <c r="C18" s="66" t="n"/>
-      <c r="D18" s="66" t="n"/>
-      <c r="E18" s="66" t="n"/>
-      <c r="F18" s="66" t="n"/>
-      <c r="G18" s="66" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="32">
-      <c r="B19" s="66" t="n"/>
-      <c r="C19" s="66" t="n"/>
-      <c r="D19" s="66" t="n"/>
-      <c r="E19" s="66" t="n"/>
-      <c r="F19" s="66" t="n"/>
-      <c r="G19" s="66" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="32">
-      <c r="B20" s="66" t="n"/>
-      <c r="C20" s="66" t="n"/>
-      <c r="D20" s="66" t="n"/>
-      <c r="E20" s="66" t="n"/>
-      <c r="F20" s="66" t="n"/>
-      <c r="G20" s="66" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="32">
-      <c r="B21" s="66" t="n"/>
-      <c r="C21" s="66" t="n"/>
-      <c r="D21" s="66" t="n"/>
-      <c r="E21" s="66" t="n"/>
-      <c r="F21" s="66" t="n"/>
-      <c r="G21" s="66" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="32">
-      <c r="B22" s="66" t="n"/>
-      <c r="C22" s="66" t="n"/>
-      <c r="D22" s="66" t="n"/>
-      <c r="E22" s="66" t="n"/>
-      <c r="F22" s="66" t="n"/>
-      <c r="G22" s="66" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="32">
-      <c r="B23" s="66" t="n"/>
-      <c r="C23" s="66" t="n"/>
-      <c r="D23" s="66" t="n"/>
-      <c r="E23" s="66" t="n"/>
-      <c r="F23" s="66" t="n"/>
-      <c r="G23" s="66" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="32">
-      <c r="B24" s="66" t="n"/>
-      <c r="C24" s="66" t="n"/>
-      <c r="D24" s="66" t="n"/>
-      <c r="E24" s="66" t="n"/>
-      <c r="F24" s="66" t="n"/>
-      <c r="G24" s="66" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="32">
-      <c r="B25" s="66" t="n"/>
-      <c r="C25" s="66" t="n"/>
-      <c r="D25" s="66" t="n"/>
-      <c r="E25" s="66" t="n"/>
-      <c r="F25" s="66" t="n"/>
-      <c r="G25" s="66" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="32">
-      <c r="B26" s="66" t="n"/>
-      <c r="C26" s="66" t="n"/>
-      <c r="D26" s="66" t="n"/>
-      <c r="E26" s="66" t="n"/>
-      <c r="F26" s="66" t="n"/>
-      <c r="G26" s="66" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="32">
-      <c r="B27" s="66" t="n"/>
-      <c r="C27" s="66" t="n"/>
-      <c r="D27" s="66" t="n"/>
-      <c r="E27" s="66" t="n"/>
-      <c r="F27" s="66" t="n"/>
-      <c r="G27" s="66" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="32">
-      <c r="B28" s="66" t="n"/>
-      <c r="C28" s="66" t="n"/>
-      <c r="D28" s="66" t="n"/>
-      <c r="E28" s="66" t="n"/>
-      <c r="F28" s="66" t="n"/>
-      <c r="G28" s="66" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="32">
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="66" t="n"/>
-      <c r="D29" s="66" t="n"/>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="66" t="n"/>
-      <c r="G29" s="66" t="n"/>
+    <row r="5">
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="29" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="29" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="29" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="29" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="29" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="29" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="29" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="29" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="29" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="29" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="29" t="n"/>
+      <c r="G24" s="29" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="29" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="29" t="n"/>
+      <c r="G28" s="29" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="29" t="n"/>
+      <c r="G29" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2157,133 +2067,133 @@
   <dimension ref="B2:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="32" min="2" max="2"/>
-    <col width="48" customWidth="1" style="32" min="3" max="3"/>
-    <col width="24" customWidth="1" style="32" min="4" max="4"/>
-    <col width="34" customWidth="1" style="32" min="5" max="5"/>
-    <col width="20" customWidth="1" style="32" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Fixed Income &amp; Rates — Institutional Decision Surface</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>Fixed Income &amp; Rates</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Declared maturity</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Canonical builder</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>tools/builders/build_fixed_income_release.py</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>Decision arena</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>trading desk, portfolio management, treasury, ALCO and independent risk</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Committee artifact</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>curve, carry and risk pack</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Operating cadence</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>intraday desk; daily risk; monthly ALCO</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Key decision outputs</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="44" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E13" s="44" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F13" s="44" t="inlineStr">
+      <c r="F13" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2375,34 +2285,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Insider questions</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="44" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D21" s="44" t="inlineStr">
+      <c r="D21" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E21" s="44" t="inlineStr">
+      <c r="E21" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F21" s="44" t="inlineStr">
+      <c r="F21" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2494,34 +2404,34 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="43" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Scenario families</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="44" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C29" s="44" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D29" s="44" t="inlineStr">
+      <c r="D29" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E29" s="44" t="inlineStr">
+      <c r="E29" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F29" s="44" t="inlineStr">
+      <c r="F29" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2613,34 +2523,34 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="43" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>Primary diligence documents</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="44" t="inlineStr">
+      <c r="B37" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="44" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D37" s="44" t="inlineStr">
+      <c r="D37" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E37" s="44" t="inlineStr">
+      <c r="E37" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F37" s="44" t="inlineStr">
+      <c r="F37" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2732,34 +2642,34 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="43" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>Challenge tests</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="44" t="inlineStr">
+      <c r="B45" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C45" s="44" t="inlineStr">
+      <c r="C45" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D45" s="44" t="inlineStr">
+      <c r="D45" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E45" s="44" t="inlineStr">
+      <c r="E45" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F45" s="44" t="inlineStr">
+      <c r="F45" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2851,34 +2761,34 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="43" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>Known failure modes</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="44" t="inlineStr">
+      <c r="B53" s="34" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="44" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D53" s="44" t="inlineStr">
+      <c r="D53" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E53" s="44" t="inlineStr">
+      <c r="E53" s="34" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F53" s="44" t="inlineStr">
+      <c r="F53" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2970,34 +2880,34 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="43" t="inlineStr">
+      <c r="B60" s="33" t="inlineStr">
         <is>
           <t>Regulatory / methodological anchors</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="44" t="inlineStr">
+      <c r="B61" s="34" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C61" s="44" t="inlineStr">
+      <c r="C61" s="34" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D61" s="44" t="inlineStr">
+      <c r="D61" s="34" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="E61" s="44" t="inlineStr">
+      <c r="E61" s="34" t="inlineStr">
         <is>
           <t>Applicability</t>
         </is>
       </c>
-      <c r="F61" s="44" t="inlineStr">
+      <c r="F61" s="34" t="inlineStr">
         <is>
           <t>Review note</t>
         </is>
@@ -3123,60 +3033,60 @@
   <dimension ref="B2:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="32" min="2" max="2"/>
-    <col width="22" customWidth="1" style="32" min="3" max="3"/>
-    <col width="52" customWidth="1" style="32" min="4" max="4"/>
-    <col width="46" customWidth="1" style="32" min="5" max="5"/>
-    <col width="36" customWidth="1" style="32" min="6" max="6"/>
-    <col width="14" customWidth="1" style="32" min="7" max="7"/>
-    <col width="18" customWidth="1" style="32" min="8" max="8"/>
-    <col width="14" customWidth="1" style="32" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Independent Challenge, Override and Closure Log</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D4" s="44" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Challenge</t>
         </is>
       </c>
-      <c r="E4" s="44" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>Owner response</t>
         </is>
       </c>
-      <c r="F4" s="44" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="44" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="H4" s="44" t="inlineStr">
+      <c r="H4" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="44" t="inlineStr">
+      <c r="I4" s="34" t="inlineStr">
         <is>
           <t>Closure</t>
         </is>
@@ -3297,66 +3207,66 @@
   <dimension ref="B2:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="32" min="2" max="2"/>
-    <col width="18" customWidth="1" style="32" min="3" max="3"/>
-    <col width="42" customWidth="1" style="32" min="4" max="4"/>
-    <col width="24" customWidth="1" style="32" min="5" max="5"/>
-    <col width="18" customWidth="1" style="32" min="6" max="6"/>
-    <col width="22" customWidth="1" style="32" min="7" max="7"/>
-    <col width="42" customWidth="1" style="32" min="8" max="8"/>
-    <col width="30" customWidth="1" style="32" min="9" max="9"/>
-    <col width="15" customWidth="1" style="32" min="10" max="10"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Source, Transformation, Ownership and Refresh Map</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Source class</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Cadence</t>
         </is>
       </c>
-      <c r="D4" s="44" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E4" s="44" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>System / provider</t>
         </is>
       </c>
-      <c r="F4" s="44" t="inlineStr">
+      <c r="F4" s="34" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="G4" s="44" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="44" t="inlineStr">
+      <c r="H4" s="34" t="inlineStr">
         <is>
           <t>Transform</t>
         </is>
       </c>
-      <c r="I4" s="44" t="inlineStr">
+      <c r="I4" s="34" t="inlineStr">
         <is>
           <t>Downstream</t>
         </is>
       </c>
-      <c r="J4" s="44" t="inlineStr">
+      <c r="J4" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3485,268 +3395,270 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="36" customWidth="1" style="31" min="2" max="2"/>
-    <col width="15" customWidth="1" style="31" min="3" max="5"/>
-    <col width="30" customWidth="1" style="31" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Pricing and Risk Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Units / note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Face value</t>
         </is>
       </c>
-      <c r="C5" s="46" t="n">
+      <c r="C5" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="D5" s="46" t="n">
+      <c r="D5" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="10">
         <f>IF(Cover!$C$9="Downside",D5,C5)</f>
         <v/>
       </c>
-      <c r="F5" s="31" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Coupon rate</t>
         </is>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="12">
         <f>IF(Cover!$C$9="Downside",D6,C6)</f>
         <v/>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Yield to maturity</t>
         </is>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="11" t="n">
         <v>0.055</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="11" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="12">
         <f>IF(Cover!$C$9="Downside",D7,C7)</f>
         <v/>
       </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Maturity</t>
         </is>
       </c>
-      <c r="C8" s="50" t="n">
+      <c r="C8" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="50" t="n">
+      <c r="D8" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="14">
         <f>IF(Cover!$C$9="Downside",D8,C8)</f>
         <v/>
       </c>
-      <c r="F8" s="31" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Coupon frequency</t>
         </is>
       </c>
-      <c r="C9" s="52" t="n">
+      <c r="C9" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="16">
         <f>IF(Cover!$C$9="Downside",D9,C9)</f>
         <v/>
       </c>
-      <c r="F9" s="31" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>per year</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Parallel yield shock</t>
         </is>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="12">
         <f>IF(Cover!$C$9="Downside",D10,C10)</f>
         <v/>
       </c>
-      <c r="F10" s="31" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="31" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>One-basis-point bump</t>
         </is>
       </c>
-      <c r="C11" s="54" t="n">
+      <c r="C11" s="17" t="n">
         <v>0.0001</v>
       </c>
-      <c r="D11" s="54" t="n">
+      <c r="D11" s="17" t="n">
         <v>0.0001</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="18">
         <f>IF(Cover!$C$9="Downside",D11,C11)</f>
         <v/>
       </c>
-      <c r="F11" s="31" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="31" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Holding period</t>
         </is>
       </c>
-      <c r="C12" s="50" t="n">
+      <c r="C12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="50" t="n">
+      <c r="D12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="14">
         <f>IF(Cover!$C$9="Downside",D12,C12)</f>
         <v/>
       </c>
-      <c r="F12" s="31" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="31" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Financing / repo rate</t>
         </is>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="11" t="n">
         <v>0.045</v>
       </c>
-      <c r="D13" s="48" t="n">
+      <c r="D13" s="11" t="n">
         <v>0.06</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="12">
         <f>IF(Cover!$C$9="Downside",D13,C13)</f>
         <v/>
       </c>
-      <c r="F13" s="31" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="31" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Position market value</t>
         </is>
       </c>
-      <c r="C14" s="56" t="n">
+      <c r="C14" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="D14" s="56" t="n">
+      <c r="D14" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="20">
         <f>IF(Cover!$C$9="Downside",D14,C14)</f>
         <v/>
       </c>
-      <c r="F14" s="31" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
@@ -3756,293 +3668,293 @@
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="14" customWidth="1" style="31" min="2" max="2"/>
-    <col width="16" customWidth="1" style="31" min="3" max="5"/>
-    <col width="18" customWidth="1" style="31" min="6" max="6"/>
-    <col width="16" customWidth="1" style="31" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Zero Curve and Discount Factors</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Tenor</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Base zero</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Downside zero</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Active zero</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>1Y forward</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="58" t="n">
+    <row r="5">
+      <c r="B5" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="11" t="n">
         <v>0.048</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D5" s="11" t="n">
         <v>0.053</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="12">
         <f>IF(Cover!$C$9="Downside",D5,C5)</f>
         <v/>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="22">
         <f>EXP(-E5*B5)</f>
         <v/>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="12">
         <f>E5</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="58" t="n">
+    <row r="6">
+      <c r="B6" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="11" t="n">
         <v>0.047</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="11" t="n">
         <v>0.052</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="12">
         <f>IF(Cover!$C$9="Downside",D6,C6)</f>
         <v/>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="22">
         <f>EXP(-E6*B6)</f>
         <v/>
       </c>
-      <c r="G6" s="49">
+      <c r="G6" s="12">
         <f>IFERROR(-LN(F6/F5)/(B6-B5),0)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="58" t="n">
+    <row r="7">
+      <c r="B7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="11" t="n">
         <v>0.045</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="12">
         <f>IF(Cover!$C$9="Downside",D7,C7)</f>
         <v/>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="22">
         <f>EXP(-E7*B7)</f>
         <v/>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="12">
         <f>IFERROR(-LN(F7/F6)/(B7-B6),0)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="58" t="n">
+    <row r="8">
+      <c r="B8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="11" t="n">
         <v>0.043</v>
       </c>
-      <c r="D8" s="48" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="E8" s="49">
+      <c r="D8" s="11" t="n">
+        <v>0.04799999999999999</v>
+      </c>
+      <c r="E8" s="12">
         <f>IF(Cover!$C$9="Downside",D8,C8)</f>
         <v/>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="22">
         <f>EXP(-E8*B8)</f>
         <v/>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="12">
         <f>IFERROR(-LN(F8/F7)/(B8-B7),0)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="58" t="n">
+    <row r="9">
+      <c r="B9" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="11" t="n">
         <v>0.042</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="11" t="n">
         <v>0.047</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="12">
         <f>IF(Cover!$C$9="Downside",D9,C9)</f>
         <v/>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="22">
         <f>EXP(-E9*B9)</f>
         <v/>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="12">
         <f>IFERROR(-LN(F9/F8)/(B9-B8),0)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="58" t="n">
+    <row r="10">
+      <c r="B10" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="11" t="n">
         <v>0.043</v>
       </c>
-      <c r="D10" s="48" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E10" s="49">
+      <c r="D10" s="11" t="n">
+        <v>0.05499999999999999</v>
+      </c>
+      <c r="E10" s="12">
         <f>IF(Cover!$C$9="Downside",D10,C10)</f>
         <v/>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="22">
         <f>EXP(-E10*B10)</f>
         <v/>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="12">
         <f>IFERROR(-LN(F10/F9)/(B10-B9),0)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="58" t="n">
+    <row r="11">
+      <c r="B11" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="48" t="n">
+      <c r="C11" s="11" t="n">
         <v>0.045</v>
       </c>
-      <c r="D11" s="48" t="n">
+      <c r="D11" s="11" t="n">
         <v>0.057</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="12">
         <f>IF(Cover!$C$9="Downside",D11,C11)</f>
         <v/>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="22">
         <f>EXP(-E11*B11)</f>
         <v/>
       </c>
-      <c r="G11" s="49">
+      <c r="G11" s="12">
         <f>IFERROR(-LN(F11/F10)/(B11-B10),0)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="58" t="n">
+    <row r="12">
+      <c r="B12" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="11" t="n">
         <v>0.047</v>
       </c>
-      <c r="D12" s="48" t="n">
+      <c r="D12" s="11" t="n">
         <v>0.059</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="12">
         <f>IF(Cover!$C$9="Downside",D12,C12)</f>
         <v/>
       </c>
-      <c r="F12" s="59">
+      <c r="F12" s="22">
         <f>EXP(-E12*B12)</f>
         <v/>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="12">
         <f>IFERROR(-LN(F12/F11)/(B12-B11),0)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="58" t="n">
+    <row r="13">
+      <c r="B13" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="11" t="n">
         <v>0.049</v>
       </c>
-      <c r="D13" s="48" t="n">
+      <c r="D13" s="11" t="n">
         <v>0.061</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="12">
         <f>IF(Cover!$C$9="Downside",D13,C13)</f>
         <v/>
       </c>
-      <c r="F13" s="59">
+      <c r="F13" s="22">
         <f>EXP(-E13*B13)</f>
         <v/>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="12">
         <f>IFERROR(-LN(F13/F12)/(B13-B12),0)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="58" t="n">
+    <row r="14">
+      <c r="B14" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="D14" s="48" t="n">
+      <c r="D14" s="11" t="n">
         <v>0.062</v>
       </c>
-      <c r="E14" s="49">
+      <c r="E14" s="12">
         <f>IF(Cover!$C$9="Downside",D14,C14)</f>
         <v/>
       </c>
-      <c r="F14" s="59">
+      <c r="F14" s="22">
         <f>EXP(-E14*B14)</f>
         <v/>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="12">
         <f>IFERROR(-LN(F14/F13)/(B14-B13),0)</f>
         <v/>
       </c>
@@ -4051,262 +3963,260 @@
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="34" customWidth="1" style="31" min="2" max="2"/>
-    <col width="18" customWidth="1" style="31" min="3" max="3"/>
-    <col width="16" customWidth="1" style="31" min="4" max="4"/>
-    <col width="44" customWidth="1" style="31" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Bond Price, Duration, and Convexity</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="10">
         <f>-PV(Assumptions!E7/Assumptions!E9,Assumptions!E8*Assumptions!E9,Assumptions!E5*Assumptions!E6/Assumptions!E9,Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>coupon annuity plus principal</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Price +1bp</t>
         </is>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="10">
         <f>-PV((Assumptions!E7+Assumptions!E11)/Assumptions!E9,Assumptions!E8*Assumptions!E9,Assumptions!E5*Assumptions!E6/Assumptions!E9,Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>finite difference</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Price -1bp</t>
         </is>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="10">
         <f>-PV((Assumptions!E7-Assumptions!E11)/Assumptions!E9,Assumptions!E8*Assumptions!E9,Assumptions!E5*Assumptions!E6/Assumptions!E9,Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>finite difference</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Numerical modified duration</t>
         </is>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="23">
         <f>IFERROR((C7-C6)/(2*C5*Assumptions!E11),0)</f>
         <v/>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>central difference</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Numerical convexity</t>
         </is>
       </c>
-      <c r="C9" s="60">
+      <c r="C9" s="23">
         <f>IFERROR((C6+C7-2*C5)/(C5*Assumptions!E11^2),0)</f>
         <v/>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>years^2</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>second difference</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>DV01</t>
         </is>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="10">
         <f>(C7-C6)/2</f>
         <v/>
       </c>
-      <c r="D10" s="31" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E10" s="31" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>price value of 1bp</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="32">
-      <c r="B11" s="31" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Current yield</t>
         </is>
       </c>
-      <c r="C11" s="49">
+      <c r="C11" s="12">
         <f>Assumptions!E5*Assumptions!E6/C5</f>
         <v/>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>annual coupon / price</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="31" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Price under parallel shock</t>
         </is>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="10">
         <f>-PV((Assumptions!E7+Assumptions!E10)/Assumptions!E9,Assumptions!E8*Assumptions!E9,Assumptions!E5*Assumptions!E6/Assumptions!E9,Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="D12" s="31" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E12" s="31" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>full repricing</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="32">
-      <c r="B13" s="31" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Duration-convexity estimate</t>
         </is>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="10">
         <f>C5*(1-C8*Assumptions!E10+0.5*C9*Assumptions!E10^2)</f>
         <v/>
       </c>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>second-order approximation</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="32">
-      <c r="B14" s="31" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Approximation residual</t>
         </is>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="10">
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="31" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="E14" s="31" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>full price less estimate</t>
         </is>
@@ -4316,630 +4226,636 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:L12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="24" customWidth="1" style="31" min="2" max="2"/>
-    <col width="16" customWidth="1" style="31" min="3" max="3"/>
-    <col width="13" customWidth="1" style="31" min="4" max="6"/>
-    <col width="14" customWidth="1" style="31" min="7" max="11"/>
-    <col width="16" customWidth="1" style="31" min="12" max="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Fixed-Income Portfolio Analytics</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Market value</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Coupon</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Maturity</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Spread duration</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Mod duration</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Convexity</t>
         </is>
       </c>
-      <c r="K4" s="45" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>DV01</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="50" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>2Y Treasury</t>
         </is>
       </c>
-      <c r="C5" s="56" t="n">
+      <c r="C5" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D5" s="11" t="n">
         <v>0.045</v>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="11" t="n">
         <v>0.044</v>
       </c>
-      <c r="F5" s="50" t="n">
+      <c r="F5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="50" t="n">
+      <c r="G5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="47">
+      <c r="H5" s="10">
         <f>-PV(E5/2,F5*2,100*D5/2,100)</f>
         <v/>
       </c>
-      <c r="I5" s="60">
+      <c r="I5" s="23">
         <f>IFERROR(((-PV((E5-0.0001)/2,F5*2,100*D5/2,100))-(-PV((E5+0.0001)/2,F5*2,100*D5/2,100)))/(2*H5*0.0001),0)</f>
         <v/>
       </c>
-      <c r="J5" s="60">
+      <c r="J5" s="23">
         <f>IFERROR(((-PV((E5+0.0001)/2,F5*2,100*D5/2,100))+(-PV((E5-0.0001)/2,F5*2,100*D5/2,100))-2*H5)/(H5*0.0001^2),0)</f>
         <v/>
       </c>
-      <c r="K5" s="57">
+      <c r="K5" s="20">
         <f>C5*I5*0.0001</f>
         <v/>
       </c>
-      <c r="L5" s="60" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="50" t="inlineStr">
+      <c r="L5" s="23" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>5Y Treasury</t>
         </is>
       </c>
-      <c r="C6" s="56" t="n">
+      <c r="C6" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="48" t="n">
+      <c r="D6" s="11" t="n">
         <v>0.043</v>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="11" t="n">
         <v>0.045</v>
       </c>
-      <c r="F6" s="50" t="n">
+      <c r="F6" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="50" t="n">
+      <c r="G6" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="47">
+      <c r="H6" s="10">
         <f>-PV(E6/2,F6*2,100*D6/2,100)</f>
         <v/>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="23">
         <f>IFERROR(((-PV((E6-0.0001)/2,F6*2,100*D6/2,100))-(-PV((E6+0.0001)/2,F6*2,100*D6/2,100)))/(2*H6*0.0001),0)</f>
         <v/>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="23">
         <f>IFERROR(((-PV((E6+0.0001)/2,F6*2,100*D6/2,100))+(-PV((E6-0.0001)/2,F6*2,100*D6/2,100))-2*H6)/(H6*0.0001^2),0)</f>
         <v/>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="20">
         <f>C6*I6*0.0001</f>
         <v/>
       </c>
-      <c r="L6" s="60" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="50" t="inlineStr">
+      <c r="L6" s="23" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>10Y Treasury</t>
         </is>
       </c>
-      <c r="C7" s="56" t="n">
+      <c r="C7" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="11" t="n">
         <v>0.055</v>
       </c>
-      <c r="F7" s="50" t="n">
+      <c r="F7" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="50" t="n">
+      <c r="G7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="47">
+      <c r="H7" s="10">
         <f>-PV(E7/2,F7*2,100*D7/2,100)</f>
         <v/>
       </c>
-      <c r="I7" s="60">
+      <c r="I7" s="23">
         <f>IFERROR(((-PV((E7-0.0001)/2,F7*2,100*D7/2,100))-(-PV((E7+0.0001)/2,F7*2,100*D7/2,100)))/(2*H7*0.0001),0)</f>
         <v/>
       </c>
-      <c r="J7" s="60">
+      <c r="J7" s="23">
         <f>IFERROR(((-PV((E7+0.0001)/2,F7*2,100*D7/2,100))+(-PV((E7-0.0001)/2,F7*2,100*D7/2,100))-2*H7)/(H7*0.0001^2),0)</f>
         <v/>
       </c>
-      <c r="K7" s="57">
+      <c r="K7" s="20">
         <f>C7*I7*0.0001</f>
         <v/>
       </c>
-      <c r="L7" s="60" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="50" t="inlineStr">
+      <c r="L7" s="23" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>IG Corporate</t>
         </is>
       </c>
-      <c r="C8" s="56" t="n">
+      <c r="C8" s="19" t="n">
         <v>45</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="D8" s="11" t="n">
         <v>0.06</v>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="11" t="n">
         <v>0.068</v>
       </c>
-      <c r="F8" s="50" t="n">
+      <c r="F8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="50" t="n">
+      <c r="G8" s="13" t="n">
         <v>5.5</v>
       </c>
-      <c r="H8" s="47">
+      <c r="H8" s="10">
         <f>-PV(E8/2,F8*2,100*D8/2,100)</f>
         <v/>
       </c>
-      <c r="I8" s="60">
+      <c r="I8" s="23">
         <f>IFERROR(((-PV((E8-0.0001)/2,F8*2,100*D8/2,100))-(-PV((E8+0.0001)/2,F8*2,100*D8/2,100)))/(2*H8*0.0001),0)</f>
         <v/>
       </c>
-      <c r="J8" s="60">
+      <c r="J8" s="23">
         <f>IFERROR(((-PV((E8+0.0001)/2,F8*2,100*D8/2,100))+(-PV((E8-0.0001)/2,F8*2,100*D8/2,100))-2*H8)/(H8*0.0001^2),0)</f>
         <v/>
       </c>
-      <c r="K8" s="57">
+      <c r="K8" s="20">
         <f>C8*I8*0.0001</f>
         <v/>
       </c>
-      <c r="L8" s="60" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="50" t="inlineStr">
+      <c r="L8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>HY Corporate</t>
         </is>
       </c>
-      <c r="C9" s="56" t="n">
+      <c r="C9" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="11" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="11" t="n">
         <v>0.105</v>
       </c>
-      <c r="F9" s="50" t="n">
+      <c r="F9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="50" t="n">
+      <c r="G9" s="13" t="n">
         <v>3.8</v>
       </c>
-      <c r="H9" s="47">
+      <c r="H9" s="10">
         <f>-PV(E9/2,F9*2,100*D9/2,100)</f>
         <v/>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="23">
         <f>IFERROR(((-PV((E9-0.0001)/2,F9*2,100*D9/2,100))-(-PV((E9+0.0001)/2,F9*2,100*D9/2,100)))/(2*H9*0.0001),0)</f>
         <v/>
       </c>
-      <c r="J9" s="60">
+      <c r="J9" s="23">
         <f>IFERROR(((-PV((E9+0.0001)/2,F9*2,100*D9/2,100))+(-PV((E9-0.0001)/2,F9*2,100*D9/2,100))-2*H9)/(H9*0.0001^2),0)</f>
         <v/>
       </c>
-      <c r="K9" s="57">
+      <c r="K9" s="20">
         <f>C9*I9*0.0001</f>
         <v/>
       </c>
-      <c r="L9" s="60" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="50" t="inlineStr">
+      <c r="L9" s="23" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Municipal</t>
         </is>
       </c>
-      <c r="C10" s="56" t="n">
+      <c r="C10" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="48" t="n">
+      <c r="D10" s="11" t="n">
         <v>0.04</v>
       </c>
-      <c r="E10" s="48" t="n">
+      <c r="E10" s="11" t="n">
         <v>0.046</v>
       </c>
-      <c r="F10" s="50" t="n">
+      <c r="F10" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="G10" s="50" t="n">
+      <c r="G10" s="13" t="n">
         <v>7.5</v>
       </c>
-      <c r="H10" s="47">
+      <c r="H10" s="10">
         <f>-PV(E10/2,F10*2,100*D10/2,100)</f>
         <v/>
       </c>
-      <c r="I10" s="60">
+      <c r="I10" s="23">
         <f>IFERROR(((-PV((E10-0.0001)/2,F10*2,100*D10/2,100))-(-PV((E10+0.0001)/2,F10*2,100*D10/2,100)))/(2*H10*0.0001),0)</f>
         <v/>
       </c>
-      <c r="J10" s="60">
+      <c r="J10" s="23">
         <f>IFERROR(((-PV((E10+0.0001)/2,F10*2,100*D10/2,100))+(-PV((E10-0.0001)/2,F10*2,100*D10/2,100))-2*H10)/(H10*0.0001^2),0)</f>
         <v/>
       </c>
-      <c r="K10" s="57">
+      <c r="K10" s="20">
         <f>C10*I10*0.0001</f>
         <v/>
       </c>
-      <c r="L10" s="60" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="61" t="inlineStr">
+      <c r="L10" s="23" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Portfolio total / weighted</t>
         </is>
       </c>
-      <c r="C12" s="62">
+      <c r="C12" s="25">
         <f>SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="D12" s="61" t="n"/>
-      <c r="E12" s="61" t="n"/>
-      <c r="F12" s="61" t="n"/>
-      <c r="G12" s="63">
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="24" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="26">
         <f>SUMPRODUCT(C5:C10,G5:G10)/SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="H12" s="61" t="n"/>
-      <c r="I12" s="63">
+      <c r="H12" s="24" t="n"/>
+      <c r="I12" s="26">
         <f>SUMPRODUCT(C5:C10,I5:I10)/SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="J12" s="63">
+      <c r="J12" s="26">
         <f>SUMPRODUCT(C5:C10,J5:J10)/SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="K12" s="62">
+      <c r="K12" s="25">
         <f>SUM(K5:K10)</f>
         <v/>
       </c>
-      <c r="L12" s="63" t="n"/>
+      <c r="L12" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:K2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="31" min="1" max="1"/>
-    <col width="24" customWidth="1" style="31" min="2" max="2"/>
-    <col width="14" customWidth="1" style="31" min="3" max="7"/>
-    <col width="16" customWidth="1" style="31" min="8" max="8"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="32">
-      <c r="B2" s="33" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Key-Rate DV01 Approximation</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="32">
-      <c r="B4" s="45" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>10Y</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>20Y</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>30Y</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Total DV01</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="32">
-      <c r="B5" s="31">
+    <row r="5">
+      <c r="B5">
         <f>Portfolio!B5</f>
         <v/>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="20">
         <f>Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-2)/MAX(2,2))</f>
         <v/>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="20">
         <f>Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-5)/MAX(2,5))</f>
         <v/>
       </c>
-      <c r="E5" s="57">
+      <c r="E5" s="20">
         <f>Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-10)/MAX(2,10))</f>
         <v/>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="20">
         <f>Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-20)/MAX(2,20))</f>
         <v/>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="20">
         <f>Portfolio!K5*MAX(0,1-ABS(Portfolio!F5-30)/MAX(2,30))</f>
         <v/>
       </c>
-      <c r="H5" s="57">
+      <c r="H5" s="20">
         <f>SUM(C5:G5)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="32">
-      <c r="B6" s="31">
+    <row r="6">
+      <c r="B6">
         <f>Portfolio!B6</f>
         <v/>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="20">
         <f>Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-2)/MAX(2,2))</f>
         <v/>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="20">
         <f>Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-5)/MAX(2,5))</f>
         <v/>
       </c>
-      <c r="E6" s="57">
+      <c r="E6" s="20">
         <f>Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-10)/MAX(2,10))</f>
         <v/>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="20">
         <f>Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-20)/MAX(2,20))</f>
         <v/>
       </c>
-      <c r="G6" s="57">
+      <c r="G6" s="20">
         <f>Portfolio!K6*MAX(0,1-ABS(Portfolio!F6-30)/MAX(2,30))</f>
         <v/>
       </c>
-      <c r="H6" s="57">
+      <c r="H6" s="20">
         <f>SUM(C6:G6)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="32">
-      <c r="B7" s="31">
+    <row r="7">
+      <c r="B7">
         <f>Portfolio!B7</f>
         <v/>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="20">
         <f>Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-2)/MAX(2,2))</f>
         <v/>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="20">
         <f>Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-5)/MAX(2,5))</f>
         <v/>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="20">
         <f>Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-10)/MAX(2,10))</f>
         <v/>
       </c>
-      <c r="F7" s="57">
+      <c r="F7" s="20">
         <f>Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-20)/MAX(2,20))</f>
         <v/>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="20">
         <f>Portfolio!K7*MAX(0,1-ABS(Portfolio!F7-30)/MAX(2,30))</f>
         <v/>
       </c>
-      <c r="H7" s="57">
+      <c r="H7" s="20">
         <f>SUM(C7:G7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="32">
-      <c r="B8" s="31">
+    <row r="8">
+      <c r="B8">
         <f>Portfolio!B8</f>
         <v/>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="20">
         <f>Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-2)/MAX(2,2))</f>
         <v/>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="20">
         <f>Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-5)/MAX(2,5))</f>
         <v/>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="20">
         <f>Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-10)/MAX(2,10))</f>
         <v/>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="20">
         <f>Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-20)/MAX(2,20))</f>
         <v/>
       </c>
-      <c r="G8" s="57">
+      <c r="G8" s="20">
         <f>Portfolio!K8*MAX(0,1-ABS(Portfolio!F8-30)/MAX(2,30))</f>
         <v/>
       </c>
-      <c r="H8" s="57">
+      <c r="H8" s="20">
         <f>SUM(C8:G8)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="32">
-      <c r="B9" s="31">
+    <row r="9">
+      <c r="B9">
         <f>Portfolio!B9</f>
         <v/>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="20">
         <f>Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-2)/MAX(2,2))</f>
         <v/>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="20">
         <f>Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-5)/MAX(2,5))</f>
         <v/>
       </c>
-      <c r="E9" s="57">
+      <c r="E9" s="20">
         <f>Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-10)/MAX(2,10))</f>
         <v/>
       </c>
-      <c r="F9" s="57">
+      <c r="F9" s="20">
         <f>Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-20)/MAX(2,20))</f>
         <v/>
       </c>
-      <c r="G9" s="57">
+      <c r="G9" s="20">
         <f>Portfolio!K9*MAX(0,1-ABS(Portfolio!F9-30)/MAX(2,30))</f>
         <v/>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="20">
         <f>SUM(C9:G9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="32">
-      <c r="B10" s="31">
+    <row r="10">
+      <c r="B10">
         <f>Portfolio!B10</f>
         <v/>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="20">
         <f>Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-2)/MAX(2,2))</f>
         <v/>
       </c>
-      <c r="D10" s="57">
+      <c r="D10" s="20">
         <f>Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-5)/MAX(2,5))</f>
         <v/>
       </c>
-      <c r="E10" s="57">
+      <c r="E10" s="20">
         <f>Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-10)/MAX(2,10))</f>
         <v/>
       </c>
-      <c r="F10" s="57">
+      <c r="F10" s="20">
         <f>Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-20)/MAX(2,20))</f>
         <v/>
       </c>
-      <c r="G10" s="57">
+      <c r="G10" s="20">
         <f>Portfolio!K10*MAX(0,1-ABS(Portfolio!F10-30)/MAX(2,30))</f>
         <v/>
       </c>
-      <c r="H10" s="57">
+      <c r="H10" s="20">
         <f>SUM(C10:G10)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="32">
-      <c r="B12" s="61" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Portfolio key-rate DV01</t>
         </is>
       </c>
-      <c r="C12" s="62">
+      <c r="C12" s="25">
         <f>SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="25">
         <f>SUM(D5:D10)</f>
         <v/>
       </c>
-      <c r="E12" s="62">
+      <c r="E12" s="25">
         <f>SUM(E5:E10)</f>
         <v/>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="25">
         <f>SUM(F5:F10)</f>
         <v/>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="25">
         <f>SUM(G5:G10)</f>
         <v/>
       </c>
-      <c r="H12" s="62">
+      <c r="H12" s="25">
         <f>SUM(H5:H10)</f>
         <v/>
       </c>
@@ -4948,8 +4864,6 @@
   <mergeCells count="1">
     <mergeCell ref="B2:H2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>